--- a/artfynd/A 20433-2025 artfynd.xlsx
+++ b/artfynd/A 20433-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125095605</v>
+        <v>125095537</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -760,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Enstaka fjäder</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125095537</v>
+        <v>125095605</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,31 +799,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -867,11 +872,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Enstaka fjäder</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 20433-2025 artfynd.xlsx
+++ b/artfynd/A 20433-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125095537</v>
+        <v>125095605</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -756,11 +760,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Enstaka fjäder</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125095605</v>
+        <v>125095537</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,35 +798,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -872,6 +867,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Enstaka fjäder</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 20433-2025 artfynd.xlsx
+++ b/artfynd/A 20433-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125095605</v>
+        <v>125095537</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>56836</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -760,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Enstaka fjäder</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125095537</v>
+        <v>125095605</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>98269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,31 +799,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -867,11 +872,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Enstaka fjäder</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 20433-2025 artfynd.xlsx
+++ b/artfynd/A 20433-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>125095537</v>
       </c>
       <c r="B2" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,12 +785,7 @@
         <v>125095605</v>
       </c>
       <c r="B3" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20433-2025 artfynd.xlsx
+++ b/artfynd/A 20433-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>125095537</v>
       </c>
       <c r="B2" t="n">
-        <v>56843</v>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>125095605</v>
       </c>
       <c r="B3" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,6 +885,218 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125096904</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stenstorp, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>462952</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6488917</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Mölltorp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125097030</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stenstorp, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>462964</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6488880</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Mölltorp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20433-2025 artfynd.xlsx
+++ b/artfynd/A 20433-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125095537</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125095605</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,6 +1006,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125096904</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,8 +1117,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125097030</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>